--- a/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>CNBB</t>
   </si>
@@ -656,107 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E8" s="3">
         <v>43500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -793,9 +799,12 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -832,9 +841,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +862,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,9 +901,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,9 +943,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -966,9 +985,12 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1005,9 +1027,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,86 +1045,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E18" s="3">
         <v>38700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>28700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>21100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,71 +1147,75 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-23400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-16000</v>
       </c>
       <c r="G20" s="3">
         <v>-16000</v>
       </c>
       <c r="H20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-15300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>16700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>12200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9100</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,9 +1228,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1231,87 +1270,96 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E23" s="3">
         <v>15200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,87 +1396,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,87 +1648,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E32" s="3">
         <v>23400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>16000</v>
       </c>
       <c r="G32" s="3">
         <v>16000</v>
       </c>
       <c r="H32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I32" s="3">
         <v>15300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,92 +1774,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,86 +1902,93 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E41" s="3">
         <v>120100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>250200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38800</v>
-      </c>
-      <c r="K41" s="3">
-        <v>26100</v>
       </c>
       <c r="L41" s="3">
         <v>26100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>26100</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1933,9 +2025,12 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1972,9 +2067,12 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2011,9 +2109,12 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2050,9 +2151,12 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2089,33 +2193,36 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E48" s="3">
         <v>9800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2128,9 +2235,12 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2152,8 +2262,8 @@
       <c r="I49" s="3">
         <v>2600</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>2600</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2167,9 +2277,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,9 +2361,12 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2284,9 +2403,12 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,48 +2445,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1246000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1165300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1148900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>937900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>737400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>662100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>621500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>569700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>502000</v>
       </c>
       <c r="L54" s="3">
         <v>502000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
+      <c r="M54" s="3">
+        <v>502000</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,32 +2526,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,27 +2565,30 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>1400</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
         <v>1400</v>
       </c>
       <c r="F58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,12 +2604,15 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2492,15 +2628,15 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,9 +2649,12 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2552,48 +2691,54 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E61" s="3">
         <v>5200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>3500</v>
       </c>
       <c r="L61" s="3">
         <v>3500</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2630,9 +2775,12 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,48 +2901,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1150400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1077200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1068000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>865900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>673700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>605500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>571500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>524200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>459700</v>
       </c>
       <c r="L66" s="3">
         <v>459700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3">
+        <v>459700</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,33 +3129,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E72" s="3">
         <v>74900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>65500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>57000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>49600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>37400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,9 +3171,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,48 +3297,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E76" s="3">
         <v>88100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>80800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>63700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>56500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>42300</v>
       </c>
       <c r="L76" s="3">
         <v>42300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
+      <c r="M76" s="3">
+        <v>42300</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,92 +3381,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,32 +3491,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>1400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
       </c>
       <c r="H83" s="3">
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,9 +3530,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,33 +3740,36 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>13800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3566,9 +3782,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,31 +3803,32 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1000</v>
       </c>
       <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>-1000</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3622,9 +3842,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,33 +3926,36 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-148700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-83200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-141200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-49900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31200</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,9 +3968,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,32 +3989,33 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>-2800</v>
       </c>
       <c r="F96" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G96" s="3">
         <v>-2700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1900</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,33 +4154,36 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>197700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>189000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>64400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>44800</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3951,9 +4196,12 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3984,39 +4232,42 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3">
         <v>-129700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>152500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25500</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4029,7 +4280,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>CNBB</t>
   </si>
@@ -1195,8 +1195,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>14700</v>
       </c>
       <c r="E21" s="3">
         <v>16700</v>
@@ -2533,7 +2533,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>21800</v>
+        <v>800</v>
       </c>
       <c r="E57" s="3">
         <v>300</v>
@@ -2574,8 +2574,8 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>1500</v>
       </c>
       <c r="E58" s="3">
         <v>1400</v>
@@ -2701,7 +2701,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>55200</v>
+        <v>3800</v>
       </c>
       <c r="E61" s="3">
         <v>5200</v>
@@ -3497,8 +3497,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
         <v>1400</v>
@@ -3749,11 +3749,11 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>13700</v>
       </c>
       <c r="E89" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="F89" s="3">
         <v>38000</v>
@@ -3809,8 +3809,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-2400</v>
       </c>
       <c r="E91" s="3">
         <v>-1900</v>
@@ -3935,8 +3935,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-115400</v>
       </c>
       <c r="E94" s="3">
         <v>-148700</v>
@@ -3996,10 +3996,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2800</v>
+        <v>-2900</v>
       </c>
       <c r="F96" s="3">
         <v>-2800</v>
@@ -4163,11 +4163,11 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>55700</v>
       </c>
       <c r="E100" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="F100" s="3">
         <v>197700</v>
@@ -4247,8 +4247,8 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-46100</v>
       </c>
       <c r="E102" s="3">
         <v>-129700</v>

--- a/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>CNBB</t>
   </si>
@@ -725,25 +725,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>57300</v>
+        <v>47800</v>
       </c>
       <c r="E8" s="3">
-        <v>43500</v>
+        <v>46600</v>
       </c>
       <c r="F8" s="3">
-        <v>38800</v>
+        <v>45200</v>
       </c>
       <c r="G8" s="3">
-        <v>35600</v>
+        <v>39500</v>
       </c>
       <c r="H8" s="3">
-        <v>32200</v>
+        <v>35100</v>
       </c>
       <c r="I8" s="3">
-        <v>28600</v>
+        <v>32000</v>
       </c>
       <c r="J8" s="3">
-        <v>25200</v>
+        <v>29200</v>
       </c>
       <c r="K8" s="3">
         <v>22800</v>
@@ -808,26 +808,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>45200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>39500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>35100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>32000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>29200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -952,26 +952,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -995,25 +995,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1052,25 +1052,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17300</v>
+        <v>34500</v>
       </c>
       <c r="E17" s="3">
-        <v>4800</v>
+        <v>31400</v>
       </c>
       <c r="F17" s="3">
-        <v>4200</v>
+        <v>30800</v>
       </c>
       <c r="G17" s="3">
-        <v>6900</v>
+        <v>26800</v>
       </c>
       <c r="H17" s="3">
-        <v>4600</v>
+        <v>23500</v>
       </c>
       <c r="I17" s="3">
-        <v>2900</v>
+        <v>21600</v>
       </c>
       <c r="J17" s="3">
-        <v>1900</v>
+        <v>20700</v>
       </c>
       <c r="K17" s="3">
         <v>1700</v>
@@ -1094,25 +1094,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>40000</v>
+        <v>13200</v>
       </c>
       <c r="E18" s="3">
-        <v>38700</v>
+        <v>15200</v>
       </c>
       <c r="F18" s="3">
-        <v>34500</v>
+        <v>14400</v>
       </c>
       <c r="G18" s="3">
-        <v>28700</v>
+        <v>12700</v>
       </c>
       <c r="H18" s="3">
-        <v>27600</v>
+        <v>11600</v>
       </c>
       <c r="I18" s="3">
-        <v>25800</v>
+        <v>10400</v>
       </c>
       <c r="J18" s="3">
-        <v>23400</v>
+        <v>8600</v>
       </c>
       <c r="K18" s="3">
         <v>21100</v>
@@ -1153,26 +1153,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-26800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-20200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-14800</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>-14000</v>
@@ -1196,25 +1196,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14700</v>
+        <v>15200</v>
       </c>
       <c r="E21" s="3">
-        <v>16700</v>
+        <v>17400</v>
       </c>
       <c r="F21" s="3">
-        <v>15400</v>
+        <v>16500</v>
       </c>
       <c r="G21" s="3">
-        <v>13500</v>
+        <v>14200</v>
       </c>
       <c r="H21" s="3">
-        <v>12200</v>
+        <v>12700</v>
       </c>
       <c r="I21" s="3">
-        <v>11000</v>
+        <v>11500</v>
       </c>
       <c r="J21" s="3">
-        <v>9100</v>
+        <v>9500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1237,26 +1237,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1657,26 +1657,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>26800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>23400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>20200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>16000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>16000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>14800</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>14000</v>
@@ -1912,22 +1912,22 @@
         <v>73800</v>
       </c>
       <c r="E41" s="3">
-        <v>120100</v>
+        <v>119900</v>
       </c>
       <c r="F41" s="3">
-        <v>250200</v>
+        <v>249500</v>
       </c>
       <c r="G41" s="3">
-        <v>100400</v>
+        <v>97100</v>
       </c>
       <c r="H41" s="3">
-        <v>61700</v>
+        <v>36100</v>
       </c>
       <c r="I41" s="3">
-        <v>54500</v>
+        <v>32500</v>
       </c>
       <c r="J41" s="3">
-        <v>64400</v>
+        <v>41300</v>
       </c>
       <c r="K41" s="3">
         <v>38800</v>
@@ -1954,22 +1954,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -1992,26 +1992,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2034,26 +2034,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2077,25 +2077,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2119,25 +2119,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>79200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>124800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>254200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>71200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>56800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>67100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>177700</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>124900</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>68400</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>28700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2245,25 +2245,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>4000</v>
       </c>
       <c r="F49" s="3">
-        <v>2600</v>
+        <v>4400</v>
       </c>
       <c r="G49" s="3">
-        <v>2600</v>
+        <v>4300</v>
       </c>
       <c r="H49" s="3">
-        <v>2600</v>
+        <v>3900</v>
       </c>
       <c r="I49" s="3">
-        <v>2600</v>
+        <v>3700</v>
       </c>
       <c r="J49" s="3">
-        <v>2600</v>
+        <v>3700</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2371,25 +2371,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>20200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2533,25 +2533,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>800</v>
+        <v>1073400</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>1063300</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>1045000</v>
       </c>
       <c r="G57" s="3">
-        <v>200</v>
+        <v>840200</v>
       </c>
       <c r="H57" s="3">
-        <v>300</v>
+        <v>652000</v>
       </c>
       <c r="I57" s="3">
-        <v>200</v>
+        <v>578900</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>544000</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2578,22 +2578,22 @@
         <v>1500</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>1300</v>
+        <v>3000</v>
       </c>
       <c r="H58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>3800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,8 +2616,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>12600</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -2631,11 +2631,11 @@
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>800</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2659,25 +2659,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1089700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1064900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1046300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>843400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>656000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>584100</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>544200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2701,25 +2701,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3800</v>
+        <v>53800</v>
       </c>
       <c r="E61" s="3">
-        <v>5200</v>
+        <v>6600</v>
       </c>
       <c r="F61" s="3">
-        <v>6600</v>
+        <v>17000</v>
       </c>
       <c r="G61" s="3">
-        <v>8000</v>
+        <v>18300</v>
       </c>
       <c r="H61" s="3">
-        <v>5800</v>
+        <v>14000</v>
       </c>
       <c r="I61" s="3">
-        <v>8100</v>
+        <v>18900</v>
       </c>
       <c r="J61" s="3">
-        <v>9200</v>
+        <v>25000</v>
       </c>
       <c r="K61" s="3">
         <v>5800</v>
@@ -2743,25 +2743,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3139,25 +3139,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>82500</v>
+        <v>83600</v>
       </c>
       <c r="E72" s="3">
-        <v>74900</v>
+        <v>75900</v>
       </c>
       <c r="F72" s="3">
-        <v>65500</v>
+        <v>66600</v>
       </c>
       <c r="G72" s="3">
-        <v>57000</v>
+        <v>57900</v>
       </c>
       <c r="H72" s="3">
-        <v>49600</v>
+        <v>50500</v>
       </c>
       <c r="I72" s="3">
-        <v>43100</v>
+        <v>44000</v>
       </c>
       <c r="J72" s="3">
-        <v>37400</v>
+        <v>37900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3996,25 +3996,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2900</v>
+        <v>2900</v>
       </c>
       <c r="F96" s="3">
-        <v>-2800</v>
+        <v>2800</v>
       </c>
       <c r="G96" s="3">
-        <v>-2700</v>
+        <v>2700</v>
       </c>
       <c r="H96" s="3">
-        <v>-2600</v>
+        <v>2200</v>
       </c>
       <c r="I96" s="3">
-        <v>-2200</v>
+        <v>2200</v>
       </c>
       <c r="J96" s="3">
-        <v>-1900</v>
+        <v>1900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4205,26 +4205,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>CNBB</t>
   </si>
@@ -656,113 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E8" s="3">
         <v>47800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>39500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>29200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,36 +808,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E10" s="3">
         <v>47800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,9 +962,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -973,8 +992,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -988,36 +1007,39 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2100</v>
       </c>
       <c r="F15" s="3">
         <v>2100</v>
       </c>
       <c r="G15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H15" s="3">
         <v>1500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1000</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1030,9 +1052,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E17" s="3">
         <v>34500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>31400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E18" s="3">
         <v>13200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,8 +1180,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,51 +1207,54 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E21" s="3">
         <v>15200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,9 +1267,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1258,8 +1297,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1273,93 +1312,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E23" s="3">
         <v>13200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E26" s="3">
         <v>10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E27" s="3">
         <v>10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4200</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,9 +1717,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1678,66 +1747,72 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E33" s="3">
         <v>10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4200</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E35" s="3">
         <v>10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4200</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,92 +1988,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E41" s="3">
         <v>73800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>249500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38800</v>
-      </c>
-      <c r="L41" s="3">
-        <v>26100</v>
       </c>
       <c r="M41" s="3">
         <v>26100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>26100</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
+        <v>100</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2013,8 +2105,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2028,35 +2120,38 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2070,36 +2165,39 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E45" s="3">
         <v>5000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2112,36 +2210,39 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>79200</v>
+        <v>77800</v>
       </c>
       <c r="E46" s="3">
+        <v>79300</v>
+      </c>
+      <c r="F46" s="3">
         <v>124800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>254200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>71200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2154,36 +2255,39 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>177700</v>
+        <v>130600</v>
       </c>
       <c r="E47" s="3">
+        <v>178100</v>
+      </c>
+      <c r="F47" s="3">
         <v>124900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24800</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2196,36 +2300,39 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,35 +2345,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>3700</v>
       </c>
       <c r="J49" s="3">
         <v>3700</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>3700</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,35 +2480,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>20200</v>
+        <v>22500</v>
       </c>
       <c r="E52" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F52" s="3">
         <v>21700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>7900</v>
       </c>
       <c r="J52" s="3">
         <v>7900</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2406,9 +2525,12 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1280300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1246000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1165300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1148900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>937900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>737400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>662100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>621500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>569700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>502000</v>
       </c>
       <c r="M54" s="3">
         <v>502000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
+      <c r="N54" s="3">
+        <v>502000</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,35 +2656,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1097100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1073400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1063300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1045000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>840200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>652000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>578900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>544000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,14 +2698,17 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1500</v>
+        <v>14700</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2584,19 +2717,19 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>3000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2607,21 +2740,24 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2652,36 +2788,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1089700</v>
+        <v>1114200</v>
       </c>
       <c r="E60" s="3">
+        <v>1088100</v>
+      </c>
+      <c r="F60" s="3">
         <v>1064900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1046300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>843400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>656000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>584100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>544200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2694,78 +2833,84 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53800</v>
+        <v>59100</v>
       </c>
       <c r="E61" s="3">
+        <v>55200</v>
+      </c>
+      <c r="F61" s="3">
         <v>6600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>3500</v>
       </c>
       <c r="M61" s="3">
         <v>3500</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6900</v>
+        <v>7300</v>
       </c>
       <c r="E62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F62" s="3">
         <v>5600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2778,9 +2923,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1180600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1150400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1077200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1068000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>865900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>673700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>605500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>571500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>524200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>459700</v>
       </c>
       <c r="M66" s="3">
         <v>459700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="N66" s="3">
+        <v>459700</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,36 +3302,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E72" s="3">
         <v>83600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>75900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>50500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>44000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>37900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E76" s="3">
         <v>95600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>88100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>80800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>63700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>56500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>50000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>42300</v>
       </c>
       <c r="M76" s="3">
         <v>42300</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>42300</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E81" s="3">
         <v>10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4200</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,35 +3689,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E83" s="3">
         <v>1400</v>
       </c>
       <c r="F83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G83" s="3">
         <v>1100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,36 +3956,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E89" s="3">
         <v>13700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3785,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,34 +4023,35 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1000</v>
       </c>
       <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>-1000</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
@@ -3845,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,36 +4155,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-115400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-148700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-83200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-141200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3971,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3999,26 +4232,26 @@
         <v>3000</v>
       </c>
       <c r="E96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F96" s="3">
         <v>2900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>2200</v>
       </c>
       <c r="I96" s="3">
         <v>2200</v>
       </c>
       <c r="J96" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K96" s="3">
         <v>1900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,36 +4399,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E100" s="3">
         <v>55700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>197700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>189000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>64400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>31500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>44800</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,9 +4444,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4226,8 +4474,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4235,42 +4483,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-46100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-129700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>152500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>46000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNBB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>CNBB</t>
   </si>
@@ -656,119 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E8" s="3">
         <v>51700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>39500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -811,39 +817,42 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E10" s="3">
         <v>51700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,9 +981,12 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -995,8 +1014,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1010,39 +1029,42 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2100</v>
       </c>
       <c r="G15" s="3">
         <v>2100</v>
       </c>
       <c r="H15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I15" s="3">
         <v>1500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1000</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
       </c>
       <c r="K15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E17" s="3">
         <v>37300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>26800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E18" s="3">
         <v>14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,8 +1213,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,54 +1243,57 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E21" s="3">
         <v>16200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>12700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,9 +1306,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1300,8 +1339,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1315,99 +1354,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E23" s="3">
         <v>14400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E26" s="3">
         <v>11600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E27" s="3">
         <v>11600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,9 +1786,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1750,69 +1819,75 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E33" s="3">
         <v>11600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E35" s="3">
         <v>11600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,98 +2074,105 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E41" s="3">
         <v>71700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>249500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38800</v>
-      </c>
-      <c r="M41" s="3">
-        <v>26100</v>
       </c>
       <c r="N41" s="3">
         <v>26100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>26100</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2108,8 +2200,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2123,9 +2215,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2135,26 +2230,26 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2168,39 +2263,42 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3">
         <v>4800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2213,39 +2311,42 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E46" s="3">
         <v>77800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>79300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>124800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>254200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>127000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>71200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>67100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2258,39 +2359,42 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E47" s="3">
         <v>130600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>178100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>124900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24800</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2303,39 +2407,42 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E48" s="3">
         <v>13000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,38 +2455,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3900</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3700</v>
       </c>
       <c r="K49" s="3">
         <v>3700</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>3700</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,38 +2599,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E52" s="3">
         <v>22500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>7900</v>
       </c>
       <c r="K52" s="3">
         <v>7900</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1319700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1280300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1246000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1165300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1148900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>937900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>737400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>662100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>621500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>569700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>502000</v>
       </c>
       <c r="N54" s="3">
         <v>502000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
+      <c r="O54" s="3">
+        <v>502000</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,38 +2786,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1117500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1097100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1073400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1063300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1045000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>840200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>652000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>578900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>544000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,17 +2831,20 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14700</v>
+        <v>27800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>37500</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2720,19 +2853,19 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>3000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2743,24 +2876,27 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>12600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,39 +2927,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1114200</v>
+        <v>1148100</v>
       </c>
       <c r="E60" s="3">
+        <v>1137000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1088100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1064900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1046300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>843400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>656000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>584100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>544200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2836,84 +2975,90 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59100</v>
+        <v>56800</v>
       </c>
       <c r="E61" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F61" s="3">
         <v>55200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5800</v>
-      </c>
-      <c r="M61" s="3">
-        <v>3500</v>
       </c>
       <c r="N61" s="3">
         <v>3500</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1212000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1180600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1150400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1077200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1068000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>865900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>673700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>605500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>571500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>524200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>459700</v>
       </c>
       <c r="N66" s="3">
         <v>459700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3">
+        <v>459700</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,39 +3475,42 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E72" s="3">
         <v>92200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>83600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>75900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>44000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>37900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,9 +3523,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>107800</v>
+      </c>
+      <c r="E76" s="3">
         <v>99600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>95600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>80800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>72000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>56500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>42300</v>
       </c>
       <c r="N76" s="3">
         <v>42300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>42300</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E81" s="3">
         <v>11600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,38 +3887,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1400</v>
       </c>
       <c r="F83" s="3">
         <v>1400</v>
       </c>
       <c r="G83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H83" s="3">
         <v>1100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>600</v>
       </c>
       <c r="J83" s="3">
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3932,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,39 +4172,42 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4220,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,37 +4243,38 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1000</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>-1000</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,39 +4384,42 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-99300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-148700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-83200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-141200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4432,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4235,26 +4468,26 @@
         <v>3000</v>
       </c>
       <c r="F96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G96" s="3">
         <v>2900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>2200</v>
       </c>
       <c r="J96" s="3">
         <v>2200</v>
       </c>
       <c r="K96" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L96" s="3">
         <v>1900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,39 +4644,42 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E100" s="3">
         <v>32000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>55700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>197700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>189000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>64400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>31500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>44800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,9 +4692,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4477,8 +4725,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4486,45 +4734,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-55700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-46100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-129700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>152500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>46000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4788,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
